--- a/documents_bin/目录模板文件.xlsx
+++ b/documents_bin/目录模板文件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\project\auto-fanban-pre\documents_bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54711D17-AB9C-43F7-A6EC-675B9901B126}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A33F0A3-7811-474C-BA31-BE2E452BD349}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,17 +21,12 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$I$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -100,9 +95,6 @@
     </r>
   </si>
   <si>
-    <t>第  图册图纸(文件)目录</t>
-  </si>
-  <si>
     <t>文件编号:</t>
   </si>
   <si>
@@ -134,6 +126,10 @@
   </si>
   <si>
     <t>附注</t>
+  </si>
+  <si>
+    <t>图纸(文件)目录</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -451,6 +447,48 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -466,53 +504,11 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -836,28 +832,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
+      <c r="B1" s="48"/>
       <c r="C1" s="9"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35" t="s">
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="51"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="10"/>
       <c r="B2" s="11"/>
       <c r="C2" s="12"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
       <c r="H2" s="13"/>
       <c r="I2" s="14"/>
     </row>
@@ -865,39 +861,39 @@
       <c r="A3" s="10"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="40"/>
+      <c r="F3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="42"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="53"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
       <c r="H4" s="16"/>
       <c r="I4" s="17"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="15"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="15"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="39"/>
+      <c r="G5" s="44"/>
       <c r="H5" s="18"/>
       <c r="I5" s="19"/>
     </row>
@@ -912,47 +908,47 @@
       <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="C7" s="36"/>
+      <c r="D7" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="46" t="s">
+      <c r="E7" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="46" t="s">
+      <c r="F7" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="G7" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="46" t="s">
+      <c r="H7" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="46" t="s">
+      <c r="I7" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="46" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="47"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="27"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="27"/>
       <c r="E9" s="28"/>
       <c r="F9" s="27"/>
@@ -962,8 +958,8 @@
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="27"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
       <c r="D10" s="27"/>
       <c r="E10" s="28"/>
       <c r="F10" s="27"/>
@@ -973,8 +969,8 @@
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="27"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
       <c r="D11" s="27"/>
       <c r="E11" s="28"/>
       <c r="F11" s="27"/>
@@ -984,8 +980,8 @@
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="27"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
       <c r="D12" s="27"/>
       <c r="E12" s="29"/>
       <c r="F12" s="27"/>
@@ -995,8 +991,8 @@
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="27"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
       <c r="D13" s="27"/>
       <c r="E13" s="29"/>
       <c r="F13" s="27"/>
@@ -1006,8 +1002,8 @@
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="27"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
       <c r="D14" s="27"/>
       <c r="E14" s="29"/>
       <c r="F14" s="27"/>
@@ -1017,8 +1013,8 @@
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="27"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
       <c r="D15" s="27"/>
       <c r="E15" s="29"/>
       <c r="F15" s="27"/>
@@ -1028,8 +1024,8 @@
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="27"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
       <c r="D16" s="27"/>
       <c r="E16" s="29"/>
       <c r="F16" s="27"/>
@@ -1039,8 +1035,8 @@
     </row>
     <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="27"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
       <c r="D17" s="27"/>
       <c r="E17" s="29"/>
       <c r="F17" s="27"/>
@@ -1050,8 +1046,8 @@
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="27"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
       <c r="D18" s="27"/>
       <c r="E18" s="29"/>
       <c r="F18" s="27"/>
@@ -1061,8 +1057,8 @@
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="27"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
       <c r="D19" s="27"/>
       <c r="E19" s="29"/>
       <c r="F19" s="27"/>
@@ -1073,8 +1069,8 @@
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="27"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
       <c r="D20" s="27"/>
       <c r="E20" s="29"/>
       <c r="F20" s="27"/>
@@ -1085,8 +1081,8 @@
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="27"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
       <c r="D21" s="27"/>
       <c r="E21" s="29"/>
       <c r="F21" s="27"/>
@@ -1096,8 +1092,8 @@
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="27"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
       <c r="D22" s="27"/>
       <c r="E22" s="29"/>
       <c r="F22" s="27"/>
@@ -1108,8 +1104,8 @@
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="27"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
       <c r="D23" s="27"/>
       <c r="E23" s="29"/>
       <c r="F23" s="27"/>
@@ -1120,8 +1116,8 @@
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="27"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
       <c r="D24" s="27"/>
       <c r="E24" s="29"/>
       <c r="F24" s="27"/>
@@ -1132,8 +1128,8 @@
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="27"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
       <c r="D25" s="27"/>
       <c r="E25" s="29"/>
       <c r="F25" s="27"/>
@@ -1143,8 +1139,8 @@
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="27"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
       <c r="D26" s="27"/>
       <c r="E26" s="29"/>
       <c r="F26" s="27"/>
@@ -1154,8 +1150,8 @@
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="27"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
       <c r="D27" s="27"/>
       <c r="E27" s="29"/>
       <c r="F27" s="27"/>
@@ -1165,8 +1161,8 @@
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="27"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
       <c r="D28" s="27"/>
       <c r="E28" s="29"/>
       <c r="F28" s="27"/>
@@ -1176,8 +1172,8 @@
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="27"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
       <c r="D29" s="27"/>
       <c r="E29" s="29"/>
       <c r="F29" s="27"/>
@@ -1187,8 +1183,8 @@
     </row>
     <row r="30" spans="1:10" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="27"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
       <c r="D30" s="27"/>
       <c r="E30" s="29"/>
       <c r="F30" s="27"/>
@@ -1199,8 +1195,8 @@
     </row>
     <row r="31" spans="1:10" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="27"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
       <c r="D31" s="27"/>
       <c r="E31" s="29"/>
       <c r="F31" s="27"/>
@@ -1210,8 +1206,8 @@
     </row>
     <row r="32" spans="1:10" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="27"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
       <c r="D32" s="27"/>
       <c r="E32" s="29"/>
       <c r="F32" s="27"/>
@@ -1221,8 +1217,8 @@
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="27"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
       <c r="D33" s="27"/>
       <c r="E33" s="29"/>
       <c r="F33" s="27"/>
@@ -1232,8 +1228,8 @@
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="27"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
       <c r="D34" s="27"/>
       <c r="E34" s="29"/>
       <c r="F34" s="27"/>
@@ -1243,8 +1239,8 @@
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="27"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
       <c r="D35" s="27"/>
       <c r="E35" s="29"/>
       <c r="F35" s="27"/>
@@ -1254,8 +1250,8 @@
     </row>
     <row r="36" spans="1:9" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="27"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
       <c r="D36" s="27"/>
       <c r="E36" s="29"/>
       <c r="F36" s="27"/>
@@ -1265,8 +1261,8 @@
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="27"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
       <c r="D37" s="27"/>
       <c r="E37" s="29"/>
       <c r="F37" s="27"/>
@@ -1276,8 +1272,8 @@
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="27"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
       <c r="D38" s="27"/>
       <c r="E38" s="29"/>
       <c r="F38" s="27"/>
@@ -1287,8 +1283,8 @@
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="27"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
       <c r="D39" s="27"/>
       <c r="E39" s="29"/>
       <c r="F39" s="27"/>
@@ -1298,8 +1294,8 @@
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="27"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="39"/>
       <c r="D40" s="27"/>
       <c r="E40" s="29"/>
       <c r="F40" s="27"/>
@@ -1309,8 +1305,8 @@
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="27"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="45"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
       <c r="D41" s="27"/>
       <c r="E41" s="29"/>
       <c r="F41" s="27"/>
@@ -1320,8 +1316,8 @@
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="27"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="45"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
       <c r="D42" s="27"/>
       <c r="E42" s="29"/>
       <c r="F42" s="27"/>
@@ -1331,8 +1327,8 @@
     </row>
     <row r="43" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="27"/>
-      <c r="B43" s="45"/>
-      <c r="C43" s="45"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="39"/>
       <c r="D43" s="27"/>
       <c r="E43" s="29"/>
       <c r="F43" s="27"/>
@@ -1342,8 +1338,8 @@
     </row>
     <row r="44" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="27"/>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="39"/>
       <c r="D44" s="27"/>
       <c r="E44" s="29"/>
       <c r="F44" s="27"/>
@@ -1353,8 +1349,8 @@
     </row>
     <row r="45" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="27"/>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="39"/>
       <c r="D45" s="27"/>
       <c r="E45" s="29"/>
       <c r="F45" s="27"/>
@@ -1364,8 +1360,8 @@
     </row>
     <row r="46" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="27"/>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
+      <c r="B46" s="39"/>
+      <c r="C46" s="39"/>
       <c r="D46" s="27"/>
       <c r="E46" s="29"/>
       <c r="F46" s="27"/>
@@ -1375,8 +1371,8 @@
     </row>
     <row r="47" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="27"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="39"/>
       <c r="D47" s="27"/>
       <c r="E47" s="29"/>
       <c r="F47" s="27"/>
@@ -1386,8 +1382,8 @@
     </row>
     <row r="48" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="27"/>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
+      <c r="B48" s="39"/>
+      <c r="C48" s="39"/>
       <c r="D48" s="27"/>
       <c r="E48" s="29"/>
       <c r="F48" s="27"/>
@@ -1397,8 +1393,8 @@
     </row>
     <row r="49" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="27"/>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
       <c r="D49" s="27"/>
       <c r="E49" s="29"/>
       <c r="F49" s="27"/>
@@ -1408,8 +1404,8 @@
     </row>
     <row r="50" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="27"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
       <c r="D50" s="27"/>
       <c r="E50" s="29"/>
       <c r="F50" s="27"/>
@@ -1419,8 +1415,8 @@
     </row>
     <row r="51" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="27"/>
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="39"/>
       <c r="D51" s="27"/>
       <c r="E51" s="29"/>
       <c r="F51" s="27"/>
@@ -1430,8 +1426,8 @@
     </row>
     <row r="52" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="27"/>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
+      <c r="B52" s="39"/>
+      <c r="C52" s="39"/>
       <c r="D52" s="27"/>
       <c r="E52" s="29"/>
       <c r="F52" s="27"/>
@@ -1441,8 +1437,8 @@
     </row>
     <row r="53" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="27"/>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
+      <c r="B53" s="39"/>
+      <c r="C53" s="39"/>
       <c r="D53" s="27"/>
       <c r="E53" s="29"/>
       <c r="F53" s="27"/>
@@ -1452,8 +1448,8 @@
     </row>
     <row r="54" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="27"/>
-      <c r="B54" s="45"/>
-      <c r="C54" s="45"/>
+      <c r="B54" s="39"/>
+      <c r="C54" s="39"/>
       <c r="D54" s="27"/>
       <c r="E54" s="29"/>
       <c r="F54" s="27"/>
@@ -1463,8 +1459,8 @@
     </row>
     <row r="55" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="27"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="39"/>
       <c r="D55" s="27"/>
       <c r="E55" s="29"/>
       <c r="F55" s="27"/>
@@ -1474,8 +1470,8 @@
     </row>
     <row r="56" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="27"/>
-      <c r="B56" s="45"/>
-      <c r="C56" s="45"/>
+      <c r="B56" s="39"/>
+      <c r="C56" s="39"/>
       <c r="D56" s="27"/>
       <c r="E56" s="29"/>
       <c r="F56" s="27"/>
@@ -1485,8 +1481,8 @@
     </row>
     <row r="57" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="27"/>
-      <c r="B57" s="45"/>
-      <c r="C57" s="45"/>
+      <c r="B57" s="39"/>
+      <c r="C57" s="39"/>
       <c r="D57" s="27"/>
       <c r="E57" s="29"/>
       <c r="F57" s="27"/>
@@ -1496,8 +1492,8 @@
     </row>
     <row r="58" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="27"/>
-      <c r="B58" s="45"/>
-      <c r="C58" s="45"/>
+      <c r="B58" s="39"/>
+      <c r="C58" s="39"/>
       <c r="D58" s="27"/>
       <c r="E58" s="29"/>
       <c r="F58" s="27"/>
@@ -1507,8 +1503,8 @@
     </row>
     <row r="59" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="27"/>
-      <c r="B59" s="45"/>
-      <c r="C59" s="45"/>
+      <c r="B59" s="39"/>
+      <c r="C59" s="39"/>
       <c r="D59" s="27"/>
       <c r="E59" s="29"/>
       <c r="F59" s="27"/>
@@ -1518,8 +1514,8 @@
     </row>
     <row r="60" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="27"/>
-      <c r="B60" s="45"/>
-      <c r="C60" s="45"/>
+      <c r="B60" s="39"/>
+      <c r="C60" s="39"/>
       <c r="D60" s="27"/>
       <c r="E60" s="29"/>
       <c r="F60" s="27"/>
@@ -1529,8 +1525,8 @@
     </row>
     <row r="61" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="27"/>
-      <c r="B61" s="45"/>
-      <c r="C61" s="45"/>
+      <c r="B61" s="39"/>
+      <c r="C61" s="39"/>
       <c r="D61" s="27"/>
       <c r="E61" s="29"/>
       <c r="F61" s="27"/>
@@ -1540,8 +1536,8 @@
     </row>
     <row r="62" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="27"/>
-      <c r="B62" s="45"/>
-      <c r="C62" s="45"/>
+      <c r="B62" s="39"/>
+      <c r="C62" s="39"/>
       <c r="D62" s="27"/>
       <c r="E62" s="29"/>
       <c r="F62" s="27"/>
@@ -1551,8 +1547,8 @@
     </row>
     <row r="63" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="27"/>
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
       <c r="D63" s="27"/>
       <c r="E63" s="29"/>
       <c r="F63" s="27"/>
@@ -1562,8 +1558,8 @@
     </row>
     <row r="64" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="27"/>
-      <c r="B64" s="45"/>
-      <c r="C64" s="45"/>
+      <c r="B64" s="39"/>
+      <c r="C64" s="39"/>
       <c r="D64" s="27"/>
       <c r="E64" s="29"/>
       <c r="F64" s="27"/>
@@ -1573,8 +1569,8 @@
     </row>
     <row r="65" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="27"/>
-      <c r="B65" s="45"/>
-      <c r="C65" s="45"/>
+      <c r="B65" s="39"/>
+      <c r="C65" s="39"/>
       <c r="D65" s="27"/>
       <c r="E65" s="29"/>
       <c r="F65" s="27"/>
@@ -1584,8 +1580,8 @@
     </row>
     <row r="66" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="27"/>
-      <c r="B66" s="45"/>
-      <c r="C66" s="45"/>
+      <c r="B66" s="39"/>
+      <c r="C66" s="39"/>
       <c r="D66" s="27"/>
       <c r="E66" s="29"/>
       <c r="F66" s="27"/>
@@ -1595,8 +1591,8 @@
     </row>
     <row r="67" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="27"/>
-      <c r="B67" s="45"/>
-      <c r="C67" s="45"/>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
       <c r="D67" s="27"/>
       <c r="E67" s="29"/>
       <c r="F67" s="27"/>
@@ -1606,8 +1602,8 @@
     </row>
     <row r="68" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="27"/>
-      <c r="B68" s="45"/>
-      <c r="C68" s="45"/>
+      <c r="B68" s="39"/>
+      <c r="C68" s="39"/>
       <c r="D68" s="27"/>
       <c r="E68" s="29"/>
       <c r="F68" s="27"/>
@@ -1617,8 +1613,8 @@
     </row>
     <row r="69" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="27"/>
-      <c r="B69" s="45"/>
-      <c r="C69" s="45"/>
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
       <c r="D69" s="27"/>
       <c r="E69" s="29"/>
       <c r="F69" s="27"/>
@@ -1628,8 +1624,8 @@
     </row>
     <row r="70" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="27"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="45"/>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
       <c r="D70" s="27"/>
       <c r="E70" s="29"/>
       <c r="F70" s="27"/>
@@ -1639,8 +1635,8 @@
     </row>
     <row r="71" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="27"/>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
       <c r="D71" s="27"/>
       <c r="E71" s="29"/>
       <c r="F71" s="27"/>
@@ -1650,8 +1646,8 @@
     </row>
     <row r="72" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="27"/>
-      <c r="B72" s="45"/>
-      <c r="C72" s="45"/>
+      <c r="B72" s="39"/>
+      <c r="C72" s="39"/>
       <c r="D72" s="27"/>
       <c r="E72" s="29"/>
       <c r="F72" s="27"/>
@@ -1661,8 +1657,8 @@
     </row>
     <row r="73" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="27"/>
-      <c r="B73" s="45"/>
-      <c r="C73" s="45"/>
+      <c r="B73" s="39"/>
+      <c r="C73" s="39"/>
       <c r="D73" s="27"/>
       <c r="E73" s="29"/>
       <c r="F73" s="27"/>
@@ -1672,8 +1668,8 @@
     </row>
     <row r="74" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="27"/>
-      <c r="B74" s="45"/>
-      <c r="C74" s="45"/>
+      <c r="B74" s="39"/>
+      <c r="C74" s="39"/>
       <c r="D74" s="27"/>
       <c r="E74" s="29"/>
       <c r="F74" s="27"/>
@@ -1683,8 +1679,8 @@
     </row>
     <row r="75" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="27"/>
-      <c r="B75" s="45"/>
-      <c r="C75" s="45"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
       <c r="D75" s="27"/>
       <c r="E75" s="29"/>
       <c r="F75" s="27"/>
@@ -1694,8 +1690,8 @@
     </row>
     <row r="76" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="27"/>
-      <c r="B76" s="45"/>
-      <c r="C76" s="45"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
       <c r="D76" s="27"/>
       <c r="E76" s="29"/>
       <c r="F76" s="27"/>
@@ -1705,8 +1701,8 @@
     </row>
     <row r="77" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="27"/>
-      <c r="B77" s="45"/>
-      <c r="C77" s="45"/>
+      <c r="B77" s="39"/>
+      <c r="C77" s="39"/>
       <c r="D77" s="27"/>
       <c r="E77" s="29"/>
       <c r="F77" s="27"/>
@@ -1716,8 +1712,8 @@
     </row>
     <row r="78" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="27"/>
-      <c r="B78" s="45"/>
-      <c r="C78" s="45"/>
+      <c r="B78" s="39"/>
+      <c r="C78" s="39"/>
       <c r="D78" s="27"/>
       <c r="E78" s="29"/>
       <c r="F78" s="27"/>
@@ -1727,8 +1723,8 @@
     </row>
     <row r="79" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="27"/>
-      <c r="B79" s="45"/>
-      <c r="C79" s="45"/>
+      <c r="B79" s="39"/>
+      <c r="C79" s="39"/>
       <c r="D79" s="27"/>
       <c r="E79" s="29"/>
       <c r="F79" s="27"/>
@@ -1738,8 +1734,8 @@
     </row>
     <row r="80" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="27"/>
-      <c r="B80" s="45"/>
-      <c r="C80" s="45"/>
+      <c r="B80" s="39"/>
+      <c r="C80" s="39"/>
       <c r="D80" s="27"/>
       <c r="E80" s="29"/>
       <c r="F80" s="27"/>
@@ -1749,8 +1745,8 @@
     </row>
     <row r="81" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="27"/>
-      <c r="B81" s="45"/>
-      <c r="C81" s="45"/>
+      <c r="B81" s="39"/>
+      <c r="C81" s="39"/>
       <c r="D81" s="27"/>
       <c r="E81" s="29"/>
       <c r="F81" s="27"/>
@@ -1760,8 +1756,8 @@
     </row>
     <row r="82" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="27"/>
-      <c r="B82" s="45"/>
-      <c r="C82" s="45"/>
+      <c r="B82" s="39"/>
+      <c r="C82" s="39"/>
       <c r="D82" s="27"/>
       <c r="E82" s="29"/>
       <c r="F82" s="27"/>
@@ -1771,8 +1767,8 @@
     </row>
     <row r="83" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="27"/>
-      <c r="B83" s="45"/>
-      <c r="C83" s="45"/>
+      <c r="B83" s="39"/>
+      <c r="C83" s="39"/>
       <c r="D83" s="27"/>
       <c r="E83" s="29"/>
       <c r="F83" s="27"/>
@@ -1782,8 +1778,8 @@
     </row>
     <row r="84" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="27"/>
-      <c r="B84" s="45"/>
-      <c r="C84" s="45"/>
+      <c r="B84" s="39"/>
+      <c r="C84" s="39"/>
       <c r="D84" s="27"/>
       <c r="E84" s="29"/>
       <c r="F84" s="27"/>
@@ -1793,8 +1789,8 @@
     </row>
     <row r="85" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="27"/>
-      <c r="B85" s="45"/>
-      <c r="C85" s="45"/>
+      <c r="B85" s="39"/>
+      <c r="C85" s="39"/>
       <c r="D85" s="27"/>
       <c r="E85" s="29"/>
       <c r="F85" s="27"/>
@@ -1804,8 +1800,8 @@
     </row>
     <row r="86" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="27"/>
-      <c r="B86" s="45"/>
-      <c r="C86" s="45"/>
+      <c r="B86" s="39"/>
+      <c r="C86" s="39"/>
       <c r="D86" s="27"/>
       <c r="E86" s="29"/>
       <c r="F86" s="27"/>
@@ -1815,8 +1811,8 @@
     </row>
     <row r="87" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="27"/>
-      <c r="B87" s="45"/>
-      <c r="C87" s="45"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
       <c r="D87" s="27"/>
       <c r="E87" s="29"/>
       <c r="F87" s="27"/>
@@ -1826,8 +1822,8 @@
     </row>
     <row r="88" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="27"/>
-      <c r="B88" s="45"/>
-      <c r="C88" s="45"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
       <c r="D88" s="27"/>
       <c r="E88" s="29"/>
       <c r="F88" s="27"/>
@@ -1837,8 +1833,8 @@
     </row>
     <row r="89" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="27"/>
-      <c r="B89" s="45"/>
-      <c r="C89" s="45"/>
+      <c r="B89" s="39"/>
+      <c r="C89" s="39"/>
       <c r="D89" s="27"/>
       <c r="E89" s="29"/>
       <c r="F89" s="27"/>
@@ -1848,8 +1844,8 @@
     </row>
     <row r="90" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="27"/>
-      <c r="B90" s="45"/>
-      <c r="C90" s="45"/>
+      <c r="B90" s="39"/>
+      <c r="C90" s="39"/>
       <c r="D90" s="27"/>
       <c r="E90" s="29"/>
       <c r="F90" s="27"/>
@@ -1859,8 +1855,8 @@
     </row>
     <row r="91" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="27"/>
-      <c r="B91" s="45"/>
-      <c r="C91" s="45"/>
+      <c r="B91" s="39"/>
+      <c r="C91" s="39"/>
       <c r="D91" s="27"/>
       <c r="E91" s="29"/>
       <c r="F91" s="27"/>
@@ -1870,8 +1866,8 @@
     </row>
     <row r="92" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="27"/>
-      <c r="B92" s="45"/>
-      <c r="C92" s="45"/>
+      <c r="B92" s="39"/>
+      <c r="C92" s="39"/>
       <c r="D92" s="27"/>
       <c r="E92" s="29"/>
       <c r="F92" s="27"/>
@@ -1881,8 +1877,8 @@
     </row>
     <row r="93" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="27"/>
-      <c r="B93" s="45"/>
-      <c r="C93" s="45"/>
+      <c r="B93" s="39"/>
+      <c r="C93" s="39"/>
       <c r="D93" s="27"/>
       <c r="E93" s="29"/>
       <c r="F93" s="27"/>
@@ -1892,8 +1888,8 @@
     </row>
     <row r="94" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="27"/>
-      <c r="B94" s="45"/>
-      <c r="C94" s="45"/>
+      <c r="B94" s="39"/>
+      <c r="C94" s="39"/>
       <c r="D94" s="27"/>
       <c r="E94" s="29"/>
       <c r="F94" s="27"/>
@@ -1903,8 +1899,8 @@
     </row>
     <row r="95" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="27"/>
-      <c r="B95" s="45"/>
-      <c r="C95" s="45"/>
+      <c r="B95" s="39"/>
+      <c r="C95" s="39"/>
       <c r="D95" s="27"/>
       <c r="E95" s="29"/>
       <c r="F95" s="27"/>
@@ -1914,8 +1910,8 @@
     </row>
     <row r="96" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="27"/>
-      <c r="B96" s="45"/>
-      <c r="C96" s="45"/>
+      <c r="B96" s="39"/>
+      <c r="C96" s="39"/>
       <c r="D96" s="27"/>
       <c r="E96" s="29"/>
       <c r="F96" s="27"/>
@@ -1925,8 +1921,8 @@
     </row>
     <row r="97" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="27"/>
-      <c r="B97" s="45"/>
-      <c r="C97" s="45"/>
+      <c r="B97" s="39"/>
+      <c r="C97" s="39"/>
       <c r="D97" s="27"/>
       <c r="E97" s="29"/>
       <c r="F97" s="27"/>
@@ -1936,8 +1932,8 @@
     </row>
     <row r="98" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="27"/>
-      <c r="B98" s="45"/>
-      <c r="C98" s="45"/>
+      <c r="B98" s="39"/>
+      <c r="C98" s="39"/>
       <c r="D98" s="27"/>
       <c r="E98" s="29"/>
       <c r="F98" s="27"/>
@@ -1947,8 +1943,8 @@
     </row>
     <row r="99" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="27"/>
-      <c r="B99" s="45"/>
-      <c r="C99" s="45"/>
+      <c r="B99" s="39"/>
+      <c r="C99" s="39"/>
       <c r="D99" s="27"/>
       <c r="E99" s="29"/>
       <c r="F99" s="27"/>
@@ -1958,8 +1954,8 @@
     </row>
     <row r="100" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="27"/>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
+      <c r="B100" s="39"/>
+      <c r="C100" s="39"/>
       <c r="D100" s="27"/>
       <c r="E100" s="29"/>
       <c r="F100" s="27"/>
@@ -1969,8 +1965,8 @@
     </row>
     <row r="101" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="27"/>
-      <c r="B101" s="45"/>
-      <c r="C101" s="45"/>
+      <c r="B101" s="39"/>
+      <c r="C101" s="39"/>
       <c r="D101" s="27"/>
       <c r="E101" s="29"/>
       <c r="F101" s="27"/>
@@ -1980,8 +1976,8 @@
     </row>
     <row r="102" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="27"/>
-      <c r="B102" s="45"/>
-      <c r="C102" s="45"/>
+      <c r="B102" s="39"/>
+      <c r="C102" s="39"/>
       <c r="D102" s="27"/>
       <c r="E102" s="29"/>
       <c r="F102" s="27"/>
@@ -1991,8 +1987,8 @@
     </row>
     <row r="103" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="27"/>
-      <c r="B103" s="45"/>
-      <c r="C103" s="45"/>
+      <c r="B103" s="39"/>
+      <c r="C103" s="39"/>
       <c r="D103" s="27"/>
       <c r="E103" s="29"/>
       <c r="F103" s="27"/>
@@ -2002,8 +1998,8 @@
     </row>
     <row r="104" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="27"/>
-      <c r="B104" s="45"/>
-      <c r="C104" s="45"/>
+      <c r="B104" s="39"/>
+      <c r="C104" s="39"/>
       <c r="D104" s="27"/>
       <c r="E104" s="29"/>
       <c r="F104" s="27"/>
@@ -2013,8 +2009,8 @@
     </row>
     <row r="105" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="27"/>
-      <c r="B105" s="45"/>
-      <c r="C105" s="45"/>
+      <c r="B105" s="39"/>
+      <c r="C105" s="39"/>
       <c r="D105" s="27"/>
       <c r="E105" s="29"/>
       <c r="F105" s="27"/>
@@ -2024,8 +2020,8 @@
     </row>
     <row r="106" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="27"/>
-      <c r="B106" s="45"/>
-      <c r="C106" s="45"/>
+      <c r="B106" s="39"/>
+      <c r="C106" s="39"/>
       <c r="D106" s="27"/>
       <c r="E106" s="29"/>
       <c r="F106" s="27"/>
@@ -2035,8 +2031,8 @@
     </row>
     <row r="107" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="27"/>
-      <c r="B107" s="45"/>
-      <c r="C107" s="45"/>
+      <c r="B107" s="39"/>
+      <c r="C107" s="39"/>
       <c r="D107" s="27"/>
       <c r="E107" s="29"/>
       <c r="F107" s="27"/>
@@ -2046,8 +2042,8 @@
     </row>
     <row r="108" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="27"/>
-      <c r="B108" s="45"/>
-      <c r="C108" s="45"/>
+      <c r="B108" s="39"/>
+      <c r="C108" s="39"/>
       <c r="D108" s="27"/>
       <c r="E108" s="29"/>
       <c r="F108" s="27"/>
@@ -2057,8 +2053,8 @@
     </row>
     <row r="109" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="27"/>
-      <c r="B109" s="45"/>
-      <c r="C109" s="45"/>
+      <c r="B109" s="39"/>
+      <c r="C109" s="39"/>
       <c r="D109" s="27"/>
       <c r="E109" s="29"/>
       <c r="F109" s="27"/>
@@ -2068,8 +2064,8 @@
     </row>
     <row r="110" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="27"/>
-      <c r="B110" s="45"/>
-      <c r="C110" s="45"/>
+      <c r="B110" s="39"/>
+      <c r="C110" s="39"/>
       <c r="D110" s="27"/>
       <c r="E110" s="29"/>
       <c r="F110" s="27"/>
@@ -2079,8 +2075,8 @@
     </row>
     <row r="111" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="27"/>
-      <c r="B111" s="45"/>
-      <c r="C111" s="45"/>
+      <c r="B111" s="39"/>
+      <c r="C111" s="39"/>
       <c r="D111" s="27"/>
       <c r="E111" s="29"/>
       <c r="F111" s="27"/>
@@ -2090,8 +2086,8 @@
     </row>
     <row r="112" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="27"/>
-      <c r="B112" s="45"/>
-      <c r="C112" s="45"/>
+      <c r="B112" s="39"/>
+      <c r="C112" s="39"/>
       <c r="D112" s="27"/>
       <c r="E112" s="29"/>
       <c r="F112" s="27"/>
@@ -2101,8 +2097,8 @@
     </row>
     <row r="113" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="27"/>
-      <c r="B113" s="45"/>
-      <c r="C113" s="45"/>
+      <c r="B113" s="39"/>
+      <c r="C113" s="39"/>
       <c r="D113" s="27"/>
       <c r="E113" s="29"/>
       <c r="F113" s="27"/>
@@ -2112,8 +2108,8 @@
     </row>
     <row r="114" spans="1:9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="27"/>
-      <c r="B114" s="45"/>
-      <c r="C114" s="45"/>
+      <c r="B114" s="39"/>
+      <c r="C114" s="39"/>
       <c r="D114" s="27"/>
       <c r="E114" s="29"/>
       <c r="F114" s="27"/>
@@ -2123,8 +2119,8 @@
     </row>
     <row r="115" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="27"/>
-      <c r="B115" s="45"/>
-      <c r="C115" s="45"/>
+      <c r="B115" s="39"/>
+      <c r="C115" s="39"/>
       <c r="D115" s="27"/>
       <c r="E115" s="29"/>
       <c r="F115" s="27"/>
@@ -2134,8 +2130,8 @@
     </row>
     <row r="116" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="27"/>
-      <c r="B116" s="45"/>
-      <c r="C116" s="45"/>
+      <c r="B116" s="39"/>
+      <c r="C116" s="39"/>
       <c r="D116" s="27"/>
       <c r="E116" s="29"/>
       <c r="F116" s="27"/>
@@ -2145,8 +2141,8 @@
     </row>
     <row r="117" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="27"/>
-      <c r="B117" s="45"/>
-      <c r="C117" s="45"/>
+      <c r="B117" s="39"/>
+      <c r="C117" s="39"/>
       <c r="D117" s="27"/>
       <c r="E117" s="29"/>
       <c r="F117" s="27"/>
@@ -2156,8 +2152,8 @@
     </row>
     <row r="118" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="27"/>
-      <c r="B118" s="45"/>
-      <c r="C118" s="45"/>
+      <c r="B118" s="39"/>
+      <c r="C118" s="39"/>
       <c r="D118" s="27"/>
       <c r="E118" s="29"/>
       <c r="F118" s="27"/>
@@ -2167,8 +2163,8 @@
     </row>
     <row r="119" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="27"/>
-      <c r="B119" s="45"/>
-      <c r="C119" s="45"/>
+      <c r="B119" s="39"/>
+      <c r="C119" s="39"/>
       <c r="D119" s="27"/>
       <c r="E119" s="29"/>
       <c r="F119" s="27"/>
@@ -2178,8 +2174,8 @@
     </row>
     <row r="120" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="27"/>
-      <c r="B120" s="45"/>
-      <c r="C120" s="45"/>
+      <c r="B120" s="39"/>
+      <c r="C120" s="39"/>
       <c r="D120" s="27"/>
       <c r="E120" s="29"/>
       <c r="F120" s="27"/>
@@ -2189,8 +2185,8 @@
     </row>
     <row r="121" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="27"/>
-      <c r="B121" s="45"/>
-      <c r="C121" s="45"/>
+      <c r="B121" s="39"/>
+      <c r="C121" s="39"/>
       <c r="D121" s="27"/>
       <c r="E121" s="29"/>
       <c r="F121" s="27"/>
@@ -2200,8 +2196,8 @@
     </row>
     <row r="122" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="27"/>
-      <c r="B122" s="45"/>
-      <c r="C122" s="45"/>
+      <c r="B122" s="39"/>
+      <c r="C122" s="39"/>
       <c r="D122" s="27"/>
       <c r="E122" s="29"/>
       <c r="F122" s="27"/>
@@ -2211,8 +2207,8 @@
     </row>
     <row r="123" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="27"/>
-      <c r="B123" s="45"/>
-      <c r="C123" s="45"/>
+      <c r="B123" s="39"/>
+      <c r="C123" s="39"/>
       <c r="D123" s="27"/>
       <c r="E123" s="29"/>
       <c r="F123" s="27"/>
@@ -2222,8 +2218,8 @@
     </row>
     <row r="124" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="27"/>
-      <c r="B124" s="45"/>
-      <c r="C124" s="45"/>
+      <c r="B124" s="39"/>
+      <c r="C124" s="39"/>
       <c r="D124" s="27"/>
       <c r="E124" s="29"/>
       <c r="F124" s="27"/>
@@ -2233,8 +2229,8 @@
     </row>
     <row r="125" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="27"/>
-      <c r="B125" s="45"/>
-      <c r="C125" s="45"/>
+      <c r="B125" s="39"/>
+      <c r="C125" s="39"/>
       <c r="D125" s="27"/>
       <c r="E125" s="29"/>
       <c r="F125" s="27"/>
@@ -2244,8 +2240,8 @@
     </row>
     <row r="126" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="27"/>
-      <c r="B126" s="45"/>
-      <c r="C126" s="45"/>
+      <c r="B126" s="39"/>
+      <c r="C126" s="39"/>
       <c r="D126" s="27"/>
       <c r="E126" s="29"/>
       <c r="F126" s="27"/>
@@ -2255,8 +2251,8 @@
     </row>
     <row r="127" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="27"/>
-      <c r="B127" s="45"/>
-      <c r="C127" s="45"/>
+      <c r="B127" s="39"/>
+      <c r="C127" s="39"/>
       <c r="D127" s="27"/>
       <c r="E127" s="29"/>
       <c r="F127" s="27"/>
@@ -2266,8 +2262,8 @@
     </row>
     <row r="128" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="27"/>
-      <c r="B128" s="45"/>
-      <c r="C128" s="45"/>
+      <c r="B128" s="39"/>
+      <c r="C128" s="39"/>
       <c r="D128" s="27"/>
       <c r="E128" s="29"/>
       <c r="F128" s="27"/>
@@ -2277,8 +2273,8 @@
     </row>
     <row r="129" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="27"/>
-      <c r="B129" s="45"/>
-      <c r="C129" s="45"/>
+      <c r="B129" s="39"/>
+      <c r="C129" s="39"/>
       <c r="D129" s="27"/>
       <c r="E129" s="29"/>
       <c r="F129" s="27"/>
@@ -2288,8 +2284,8 @@
     </row>
     <row r="130" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="27"/>
-      <c r="B130" s="45"/>
-      <c r="C130" s="45"/>
+      <c r="B130" s="39"/>
+      <c r="C130" s="39"/>
       <c r="D130" s="27"/>
       <c r="E130" s="29"/>
       <c r="F130" s="27"/>
@@ -2299,8 +2295,8 @@
     </row>
     <row r="131" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="27"/>
-      <c r="B131" s="45"/>
-      <c r="C131" s="45"/>
+      <c r="B131" s="39"/>
+      <c r="C131" s="39"/>
       <c r="D131" s="27"/>
       <c r="E131" s="29"/>
       <c r="F131" s="27"/>
@@ -2310,8 +2306,8 @@
     </row>
     <row r="132" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="27"/>
-      <c r="B132" s="45"/>
-      <c r="C132" s="45"/>
+      <c r="B132" s="39"/>
+      <c r="C132" s="39"/>
       <c r="D132" s="27"/>
       <c r="E132" s="29"/>
       <c r="F132" s="27"/>
@@ -2321,8 +2317,8 @@
     </row>
     <row r="133" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="27"/>
-      <c r="B133" s="45"/>
-      <c r="C133" s="45"/>
+      <c r="B133" s="39"/>
+      <c r="C133" s="39"/>
       <c r="D133" s="27"/>
       <c r="E133" s="29"/>
       <c r="F133" s="27"/>
@@ -2332,8 +2328,8 @@
     </row>
     <row r="134" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="27"/>
-      <c r="B134" s="45"/>
-      <c r="C134" s="45"/>
+      <c r="B134" s="39"/>
+      <c r="C134" s="39"/>
       <c r="D134" s="27"/>
       <c r="E134" s="29"/>
       <c r="F134" s="27"/>
@@ -2343,8 +2339,8 @@
     </row>
     <row r="135" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="27"/>
-      <c r="B135" s="45"/>
-      <c r="C135" s="45"/>
+      <c r="B135" s="39"/>
+      <c r="C135" s="39"/>
       <c r="D135" s="27"/>
       <c r="E135" s="29"/>
       <c r="F135" s="27"/>
@@ -2354,8 +2350,8 @@
     </row>
     <row r="136" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="27"/>
-      <c r="B136" s="45"/>
-      <c r="C136" s="45"/>
+      <c r="B136" s="39"/>
+      <c r="C136" s="39"/>
       <c r="D136" s="27"/>
       <c r="E136" s="29"/>
       <c r="F136" s="27"/>
@@ -2365,8 +2361,8 @@
     </row>
     <row r="137" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="27"/>
-      <c r="B137" s="45"/>
-      <c r="C137" s="45"/>
+      <c r="B137" s="39"/>
+      <c r="C137" s="39"/>
       <c r="D137" s="27"/>
       <c r="E137" s="29"/>
       <c r="F137" s="27"/>
@@ -2376,8 +2372,8 @@
     </row>
     <row r="138" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="27"/>
-      <c r="B138" s="45"/>
-      <c r="C138" s="45"/>
+      <c r="B138" s="39"/>
+      <c r="C138" s="39"/>
       <c r="D138" s="27"/>
       <c r="E138" s="29"/>
       <c r="F138" s="27"/>
@@ -2387,8 +2383,8 @@
     </row>
     <row r="139" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="27"/>
-      <c r="B139" s="45"/>
-      <c r="C139" s="45"/>
+      <c r="B139" s="39"/>
+      <c r="C139" s="39"/>
       <c r="D139" s="27"/>
       <c r="E139" s="29"/>
       <c r="F139" s="27"/>
@@ -2398,8 +2394,8 @@
     </row>
     <row r="140" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="27"/>
-      <c r="B140" s="45"/>
-      <c r="C140" s="45"/>
+      <c r="B140" s="39"/>
+      <c r="C140" s="39"/>
       <c r="D140" s="27"/>
       <c r="E140" s="29"/>
       <c r="F140" s="27"/>
@@ -2409,8 +2405,8 @@
     </row>
     <row r="141" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="27"/>
-      <c r="B141" s="45"/>
-      <c r="C141" s="45"/>
+      <c r="B141" s="39"/>
+      <c r="C141" s="39"/>
       <c r="D141" s="27"/>
       <c r="E141" s="29"/>
       <c r="F141" s="27"/>
@@ -2420,8 +2416,8 @@
     </row>
     <row r="142" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="27"/>
-      <c r="B142" s="45"/>
-      <c r="C142" s="45"/>
+      <c r="B142" s="39"/>
+      <c r="C142" s="39"/>
       <c r="D142" s="27"/>
       <c r="E142" s="29"/>
       <c r="F142" s="27"/>
@@ -2431,8 +2427,8 @@
     </row>
     <row r="143" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="27"/>
-      <c r="B143" s="45"/>
-      <c r="C143" s="45"/>
+      <c r="B143" s="39"/>
+      <c r="C143" s="39"/>
       <c r="D143" s="27"/>
       <c r="E143" s="29"/>
       <c r="F143" s="27"/>
@@ -2442,8 +2438,8 @@
     </row>
     <row r="144" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="27"/>
-      <c r="B144" s="45"/>
-      <c r="C144" s="45"/>
+      <c r="B144" s="39"/>
+      <c r="C144" s="39"/>
       <c r="D144" s="27"/>
       <c r="E144" s="29"/>
       <c r="F144" s="27"/>
@@ -2453,8 +2449,8 @@
     </row>
     <row r="145" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="27"/>
-      <c r="B145" s="45"/>
-      <c r="C145" s="45"/>
+      <c r="B145" s="39"/>
+      <c r="C145" s="39"/>
       <c r="D145" s="27"/>
       <c r="E145" s="29"/>
       <c r="F145" s="27"/>
@@ -2464,8 +2460,8 @@
     </row>
     <row r="146" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="27"/>
-      <c r="B146" s="45"/>
-      <c r="C146" s="45"/>
+      <c r="B146" s="39"/>
+      <c r="C146" s="39"/>
       <c r="D146" s="27"/>
       <c r="E146" s="29"/>
       <c r="F146" s="27"/>
@@ -2475,8 +2471,8 @@
     </row>
     <row r="147" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="27"/>
-      <c r="B147" s="45"/>
-      <c r="C147" s="45"/>
+      <c r="B147" s="39"/>
+      <c r="C147" s="39"/>
       <c r="D147" s="27"/>
       <c r="E147" s="29"/>
       <c r="F147" s="27"/>
@@ -2486,8 +2482,8 @@
     </row>
     <row r="148" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="27"/>
-      <c r="B148" s="45"/>
-      <c r="C148" s="45"/>
+      <c r="B148" s="39"/>
+      <c r="C148" s="39"/>
       <c r="D148" s="27"/>
       <c r="E148" s="29"/>
       <c r="F148" s="27"/>
@@ -2497,8 +2493,8 @@
     </row>
     <row r="149" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="27"/>
-      <c r="B149" s="45"/>
-      <c r="C149" s="45"/>
+      <c r="B149" s="39"/>
+      <c r="C149" s="39"/>
       <c r="D149" s="27"/>
       <c r="E149" s="29"/>
       <c r="F149" s="27"/>
@@ -2508,8 +2504,8 @@
     </row>
     <row r="150" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="27"/>
-      <c r="B150" s="45"/>
-      <c r="C150" s="45"/>
+      <c r="B150" s="39"/>
+      <c r="C150" s="39"/>
       <c r="D150" s="27"/>
       <c r="E150" s="29"/>
       <c r="F150" s="27"/>
@@ -2519,8 +2515,8 @@
     </row>
     <row r="151" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="27"/>
-      <c r="B151" s="45"/>
-      <c r="C151" s="45"/>
+      <c r="B151" s="39"/>
+      <c r="C151" s="39"/>
       <c r="D151" s="27"/>
       <c r="E151" s="29"/>
       <c r="F151" s="27"/>
@@ -2530,8 +2526,8 @@
     </row>
     <row r="152" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="27"/>
-      <c r="B152" s="45"/>
-      <c r="C152" s="45"/>
+      <c r="B152" s="39"/>
+      <c r="C152" s="39"/>
       <c r="D152" s="27"/>
       <c r="E152" s="29"/>
       <c r="F152" s="27"/>
@@ -2541,8 +2537,8 @@
     </row>
     <row r="153" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="27"/>
-      <c r="B153" s="45"/>
-      <c r="C153" s="45"/>
+      <c r="B153" s="39"/>
+      <c r="C153" s="39"/>
       <c r="D153" s="27"/>
       <c r="E153" s="29"/>
       <c r="F153" s="27"/>
@@ -2552,8 +2548,8 @@
     </row>
     <row r="154" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="27"/>
-      <c r="B154" s="45"/>
-      <c r="C154" s="45"/>
+      <c r="B154" s="39"/>
+      <c r="C154" s="39"/>
       <c r="D154" s="27"/>
       <c r="E154" s="29"/>
       <c r="F154" s="27"/>
@@ -2563,8 +2559,8 @@
     </row>
     <row r="155" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="27"/>
-      <c r="B155" s="45"/>
-      <c r="C155" s="45"/>
+      <c r="B155" s="39"/>
+      <c r="C155" s="39"/>
       <c r="D155" s="27"/>
       <c r="E155" s="29"/>
       <c r="F155" s="27"/>
@@ -2574,8 +2570,8 @@
     </row>
     <row r="156" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="27"/>
-      <c r="B156" s="45"/>
-      <c r="C156" s="45"/>
+      <c r="B156" s="39"/>
+      <c r="C156" s="39"/>
       <c r="D156" s="27"/>
       <c r="E156" s="29"/>
       <c r="F156" s="27"/>
@@ -2585,8 +2581,8 @@
     </row>
     <row r="157" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="27"/>
-      <c r="B157" s="45"/>
-      <c r="C157" s="45"/>
+      <c r="B157" s="39"/>
+      <c r="C157" s="39"/>
       <c r="D157" s="27"/>
       <c r="E157" s="29"/>
       <c r="F157" s="27"/>
@@ -2596,8 +2592,8 @@
     </row>
     <row r="158" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="27"/>
-      <c r="B158" s="45"/>
-      <c r="C158" s="45"/>
+      <c r="B158" s="39"/>
+      <c r="C158" s="39"/>
       <c r="D158" s="27"/>
       <c r="E158" s="29"/>
       <c r="F158" s="27"/>
@@ -2607,8 +2603,8 @@
     </row>
     <row r="159" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="27"/>
-      <c r="B159" s="45"/>
-      <c r="C159" s="45"/>
+      <c r="B159" s="39"/>
+      <c r="C159" s="39"/>
       <c r="D159" s="27"/>
       <c r="E159" s="29"/>
       <c r="F159" s="27"/>
@@ -2618,8 +2614,8 @@
     </row>
     <row r="160" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="27"/>
-      <c r="B160" s="45"/>
-      <c r="C160" s="45"/>
+      <c r="B160" s="39"/>
+      <c r="C160" s="39"/>
       <c r="D160" s="27"/>
       <c r="E160" s="29"/>
       <c r="F160" s="27"/>
@@ -2629,8 +2625,8 @@
     </row>
     <row r="161" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="27"/>
-      <c r="B161" s="45"/>
-      <c r="C161" s="45"/>
+      <c r="B161" s="39"/>
+      <c r="C161" s="39"/>
       <c r="D161" s="27"/>
       <c r="E161" s="29"/>
       <c r="F161" s="27"/>
@@ -2640,8 +2636,8 @@
     </row>
     <row r="162" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="27"/>
-      <c r="B162" s="45"/>
-      <c r="C162" s="45"/>
+      <c r="B162" s="39"/>
+      <c r="C162" s="39"/>
       <c r="D162" s="27"/>
       <c r="E162" s="29"/>
       <c r="F162" s="27"/>
@@ -2651,8 +2647,8 @@
     </row>
     <row r="163" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="27"/>
-      <c r="B163" s="45"/>
-      <c r="C163" s="45"/>
+      <c r="B163" s="39"/>
+      <c r="C163" s="39"/>
       <c r="D163" s="27"/>
       <c r="E163" s="29"/>
       <c r="F163" s="27"/>
@@ -2662,8 +2658,8 @@
     </row>
     <row r="164" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="27"/>
-      <c r="B164" s="45"/>
-      <c r="C164" s="45"/>
+      <c r="B164" s="39"/>
+      <c r="C164" s="39"/>
       <c r="D164" s="27"/>
       <c r="E164" s="29"/>
       <c r="F164" s="27"/>
@@ -2673,8 +2669,8 @@
     </row>
     <row r="165" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="27"/>
-      <c r="B165" s="45"/>
-      <c r="C165" s="45"/>
+      <c r="B165" s="39"/>
+      <c r="C165" s="39"/>
       <c r="D165" s="27"/>
       <c r="E165" s="29"/>
       <c r="F165" s="27"/>
@@ -2684,8 +2680,8 @@
     </row>
     <row r="166" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="27"/>
-      <c r="B166" s="45"/>
-      <c r="C166" s="45"/>
+      <c r="B166" s="39"/>
+      <c r="C166" s="39"/>
       <c r="D166" s="27"/>
       <c r="E166" s="29"/>
       <c r="F166" s="27"/>
@@ -2695,8 +2691,8 @@
     </row>
     <row r="167" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="27"/>
-      <c r="B167" s="45"/>
-      <c r="C167" s="45"/>
+      <c r="B167" s="39"/>
+      <c r="C167" s="39"/>
       <c r="D167" s="27"/>
       <c r="E167" s="29"/>
       <c r="F167" s="27"/>
@@ -2706,8 +2702,8 @@
     </row>
     <row r="168" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="27"/>
-      <c r="B168" s="45"/>
-      <c r="C168" s="45"/>
+      <c r="B168" s="39"/>
+      <c r="C168" s="39"/>
       <c r="D168" s="27"/>
       <c r="E168" s="29"/>
       <c r="F168" s="27"/>
@@ -2717,8 +2713,8 @@
     </row>
     <row r="169" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="27"/>
-      <c r="B169" s="45"/>
-      <c r="C169" s="45"/>
+      <c r="B169" s="39"/>
+      <c r="C169" s="39"/>
       <c r="D169" s="27"/>
       <c r="E169" s="29"/>
       <c r="F169" s="27"/>
@@ -2728,8 +2724,8 @@
     </row>
     <row r="170" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="27"/>
-      <c r="B170" s="45"/>
-      <c r="C170" s="45"/>
+      <c r="B170" s="39"/>
+      <c r="C170" s="39"/>
       <c r="D170" s="27"/>
       <c r="E170" s="29"/>
       <c r="F170" s="27"/>
@@ -2739,8 +2735,8 @@
     </row>
     <row r="171" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="27"/>
-      <c r="B171" s="45"/>
-      <c r="C171" s="45"/>
+      <c r="B171" s="39"/>
+      <c r="C171" s="39"/>
       <c r="D171" s="27"/>
       <c r="E171" s="29"/>
       <c r="F171" s="27"/>
@@ -2750,8 +2746,8 @@
     </row>
     <row r="172" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="27"/>
-      <c r="B172" s="45"/>
-      <c r="C172" s="45"/>
+      <c r="B172" s="39"/>
+      <c r="C172" s="39"/>
       <c r="D172" s="27"/>
       <c r="E172" s="29"/>
       <c r="F172" s="27"/>
@@ -2761,8 +2757,8 @@
     </row>
     <row r="173" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="27"/>
-      <c r="B173" s="45"/>
-      <c r="C173" s="45"/>
+      <c r="B173" s="39"/>
+      <c r="C173" s="39"/>
       <c r="D173" s="27"/>
       <c r="E173" s="29"/>
       <c r="F173" s="27"/>
@@ -2772,8 +2768,8 @@
     </row>
     <row r="174" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="27"/>
-      <c r="B174" s="45"/>
-      <c r="C174" s="45"/>
+      <c r="B174" s="39"/>
+      <c r="C174" s="39"/>
       <c r="D174" s="27"/>
       <c r="E174" s="29"/>
       <c r="F174" s="27"/>
@@ -2783,8 +2779,8 @@
     </row>
     <row r="175" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="27"/>
-      <c r="B175" s="45"/>
-      <c r="C175" s="45"/>
+      <c r="B175" s="39"/>
+      <c r="C175" s="39"/>
       <c r="D175" s="27"/>
       <c r="E175" s="29"/>
       <c r="F175" s="27"/>
@@ -2794,8 +2790,8 @@
     </row>
     <row r="176" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="27"/>
-      <c r="B176" s="45"/>
-      <c r="C176" s="45"/>
+      <c r="B176" s="39"/>
+      <c r="C176" s="39"/>
       <c r="D176" s="27"/>
       <c r="E176" s="29"/>
       <c r="F176" s="27"/>
@@ -2805,8 +2801,8 @@
     </row>
     <row r="177" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="27"/>
-      <c r="B177" s="45"/>
-      <c r="C177" s="45"/>
+      <c r="B177" s="39"/>
+      <c r="C177" s="39"/>
       <c r="D177" s="27"/>
       <c r="E177" s="29"/>
       <c r="F177" s="27"/>
@@ -2816,8 +2812,8 @@
     </row>
     <row r="178" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="27"/>
-      <c r="B178" s="45"/>
-      <c r="C178" s="45"/>
+      <c r="B178" s="39"/>
+      <c r="C178" s="39"/>
       <c r="D178" s="27"/>
       <c r="E178" s="29"/>
       <c r="F178" s="27"/>
@@ -2827,8 +2823,8 @@
     </row>
     <row r="179" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="27"/>
-      <c r="B179" s="45"/>
-      <c r="C179" s="45"/>
+      <c r="B179" s="39"/>
+      <c r="C179" s="39"/>
       <c r="D179" s="27"/>
       <c r="E179" s="29"/>
       <c r="F179" s="27"/>
@@ -2838,8 +2834,8 @@
     </row>
     <row r="180" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="27"/>
-      <c r="B180" s="45"/>
-      <c r="C180" s="45"/>
+      <c r="B180" s="39"/>
+      <c r="C180" s="39"/>
       <c r="D180" s="27"/>
       <c r="E180" s="29"/>
       <c r="F180" s="27"/>
@@ -2849,8 +2845,8 @@
     </row>
     <row r="181" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="27"/>
-      <c r="B181" s="45"/>
-      <c r="C181" s="45"/>
+      <c r="B181" s="39"/>
+      <c r="C181" s="39"/>
       <c r="D181" s="27"/>
       <c r="E181" s="29"/>
       <c r="F181" s="27"/>
@@ -2860,8 +2856,8 @@
     </row>
     <row r="182" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="27"/>
-      <c r="B182" s="45"/>
-      <c r="C182" s="45"/>
+      <c r="B182" s="39"/>
+      <c r="C182" s="39"/>
       <c r="D182" s="27"/>
       <c r="E182" s="29"/>
       <c r="F182" s="27"/>
@@ -2871,8 +2867,8 @@
     </row>
     <row r="183" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="27"/>
-      <c r="B183" s="45"/>
-      <c r="C183" s="45"/>
+      <c r="B183" s="39"/>
+      <c r="C183" s="39"/>
       <c r="D183" s="27"/>
       <c r="E183" s="29"/>
       <c r="F183" s="27"/>
@@ -2882,8 +2878,8 @@
     </row>
     <row r="184" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="27"/>
-      <c r="B184" s="45"/>
-      <c r="C184" s="45"/>
+      <c r="B184" s="39"/>
+      <c r="C184" s="39"/>
       <c r="D184" s="27"/>
       <c r="E184" s="29"/>
       <c r="F184" s="27"/>
@@ -2893,8 +2889,8 @@
     </row>
     <row r="185" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="27"/>
-      <c r="B185" s="45"/>
-      <c r="C185" s="45"/>
+      <c r="B185" s="39"/>
+      <c r="C185" s="39"/>
       <c r="D185" s="27"/>
       <c r="E185" s="29"/>
       <c r="F185" s="27"/>
@@ -2904,8 +2900,8 @@
     </row>
     <row r="186" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="27"/>
-      <c r="B186" s="45"/>
-      <c r="C186" s="45"/>
+      <c r="B186" s="39"/>
+      <c r="C186" s="39"/>
       <c r="D186" s="27"/>
       <c r="E186" s="29"/>
       <c r="F186" s="27"/>
@@ -2915,8 +2911,8 @@
     </row>
     <row r="187" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="27"/>
-      <c r="B187" s="45"/>
-      <c r="C187" s="45"/>
+      <c r="B187" s="39"/>
+      <c r="C187" s="39"/>
       <c r="D187" s="27"/>
       <c r="E187" s="29"/>
       <c r="F187" s="27"/>
@@ -2926,8 +2922,8 @@
     </row>
     <row r="188" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="27"/>
-      <c r="B188" s="45"/>
-      <c r="C188" s="45"/>
+      <c r="B188" s="39"/>
+      <c r="C188" s="39"/>
       <c r="D188" s="27"/>
       <c r="E188" s="29"/>
       <c r="F188" s="27"/>
@@ -2937,8 +2933,8 @@
     </row>
     <row r="189" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="27"/>
-      <c r="B189" s="45"/>
-      <c r="C189" s="45"/>
+      <c r="B189" s="39"/>
+      <c r="C189" s="39"/>
       <c r="D189" s="27"/>
       <c r="E189" s="29"/>
       <c r="F189" s="27"/>
@@ -2948,8 +2944,8 @@
     </row>
     <row r="190" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="27"/>
-      <c r="B190" s="45"/>
-      <c r="C190" s="45"/>
+      <c r="B190" s="39"/>
+      <c r="C190" s="39"/>
       <c r="D190" s="27"/>
       <c r="E190" s="29"/>
       <c r="F190" s="27"/>
@@ -2959,8 +2955,8 @@
     </row>
     <row r="191" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="27"/>
-      <c r="B191" s="45"/>
-      <c r="C191" s="45"/>
+      <c r="B191" s="39"/>
+      <c r="C191" s="39"/>
       <c r="D191" s="27"/>
       <c r="E191" s="29"/>
       <c r="F191" s="27"/>
@@ -2970,8 +2966,8 @@
     </row>
     <row r="192" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="27"/>
-      <c r="B192" s="45"/>
-      <c r="C192" s="45"/>
+      <c r="B192" s="39"/>
+      <c r="C192" s="39"/>
       <c r="D192" s="27"/>
       <c r="E192" s="29"/>
       <c r="F192" s="27"/>
@@ -2981,8 +2977,8 @@
     </row>
     <row r="193" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="27"/>
-      <c r="B193" s="45"/>
-      <c r="C193" s="45"/>
+      <c r="B193" s="39"/>
+      <c r="C193" s="39"/>
       <c r="D193" s="27"/>
       <c r="E193" s="29"/>
       <c r="F193" s="27"/>
@@ -2992,8 +2988,8 @@
     </row>
     <row r="194" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="27"/>
-      <c r="B194" s="45"/>
-      <c r="C194" s="45"/>
+      <c r="B194" s="39"/>
+      <c r="C194" s="39"/>
       <c r="D194" s="27"/>
       <c r="E194" s="29"/>
       <c r="F194" s="27"/>
@@ -3003,8 +2999,8 @@
     </row>
     <row r="195" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="27"/>
-      <c r="B195" s="45"/>
-      <c r="C195" s="45"/>
+      <c r="B195" s="39"/>
+      <c r="C195" s="39"/>
       <c r="D195" s="27"/>
       <c r="E195" s="29"/>
       <c r="F195" s="27"/>
@@ -3014,8 +3010,8 @@
     </row>
     <row r="196" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="27"/>
-      <c r="B196" s="45"/>
-      <c r="C196" s="45"/>
+      <c r="B196" s="39"/>
+      <c r="C196" s="39"/>
       <c r="D196" s="27"/>
       <c r="E196" s="29"/>
       <c r="F196" s="27"/>
@@ -3025,8 +3021,8 @@
     </row>
     <row r="197" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="27"/>
-      <c r="B197" s="45"/>
-      <c r="C197" s="45"/>
+      <c r="B197" s="39"/>
+      <c r="C197" s="39"/>
       <c r="D197" s="27"/>
       <c r="E197" s="29"/>
       <c r="F197" s="27"/>
@@ -3036,8 +3032,8 @@
     </row>
     <row r="198" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="27"/>
-      <c r="B198" s="45"/>
-      <c r="C198" s="45"/>
+      <c r="B198" s="39"/>
+      <c r="C198" s="39"/>
       <c r="D198" s="27"/>
       <c r="E198" s="29"/>
       <c r="F198" s="27"/>
@@ -3047,8 +3043,8 @@
     </row>
     <row r="199" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="27"/>
-      <c r="B199" s="45"/>
-      <c r="C199" s="45"/>
+      <c r="B199" s="39"/>
+      <c r="C199" s="39"/>
       <c r="D199" s="27"/>
       <c r="E199" s="29"/>
       <c r="F199" s="27"/>
@@ -3058,8 +3054,8 @@
     </row>
     <row r="200" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="27"/>
-      <c r="B200" s="45"/>
-      <c r="C200" s="45"/>
+      <c r="B200" s="39"/>
+      <c r="C200" s="39"/>
       <c r="D200" s="27"/>
       <c r="E200" s="29"/>
       <c r="F200" s="27"/>
@@ -3069,8 +3065,8 @@
     </row>
     <row r="201" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="27"/>
-      <c r="B201" s="45"/>
-      <c r="C201" s="45"/>
+      <c r="B201" s="39"/>
+      <c r="C201" s="39"/>
       <c r="D201" s="27"/>
       <c r="E201" s="29"/>
       <c r="F201" s="27"/>
@@ -3080,8 +3076,8 @@
     </row>
     <row r="202" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="27"/>
-      <c r="B202" s="45"/>
-      <c r="C202" s="45"/>
+      <c r="B202" s="39"/>
+      <c r="C202" s="39"/>
       <c r="D202" s="27"/>
       <c r="E202" s="29"/>
       <c r="F202" s="27"/>
@@ -3091,8 +3087,8 @@
     </row>
     <row r="203" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="27"/>
-      <c r="B203" s="45"/>
-      <c r="C203" s="45"/>
+      <c r="B203" s="39"/>
+      <c r="C203" s="39"/>
       <c r="D203" s="27"/>
       <c r="E203" s="29"/>
       <c r="F203" s="27"/>
@@ -3102,8 +3098,8 @@
     </row>
     <row r="204" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="27"/>
-      <c r="B204" s="45"/>
-      <c r="C204" s="45"/>
+      <c r="B204" s="39"/>
+      <c r="C204" s="39"/>
       <c r="D204" s="27"/>
       <c r="E204" s="29"/>
       <c r="F204" s="27"/>
@@ -3113,8 +3109,8 @@
     </row>
     <row r="205" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="27"/>
-      <c r="B205" s="45"/>
-      <c r="C205" s="45"/>
+      <c r="B205" s="39"/>
+      <c r="C205" s="39"/>
       <c r="D205" s="27"/>
       <c r="E205" s="29"/>
       <c r="F205" s="27"/>
@@ -3124,8 +3120,8 @@
     </row>
     <row r="206" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="27"/>
-      <c r="B206" s="45"/>
-      <c r="C206" s="45"/>
+      <c r="B206" s="39"/>
+      <c r="C206" s="39"/>
       <c r="D206" s="27"/>
       <c r="E206" s="29"/>
       <c r="F206" s="27"/>
@@ -3135,8 +3131,8 @@
     </row>
     <row r="207" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="27"/>
-      <c r="B207" s="45"/>
-      <c r="C207" s="45"/>
+      <c r="B207" s="39"/>
+      <c r="C207" s="39"/>
       <c r="D207" s="27"/>
       <c r="E207" s="29"/>
       <c r="F207" s="27"/>
@@ -3146,8 +3142,8 @@
     </row>
     <row r="208" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="27"/>
-      <c r="B208" s="45"/>
-      <c r="C208" s="45"/>
+      <c r="B208" s="39"/>
+      <c r="C208" s="39"/>
       <c r="D208" s="27"/>
       <c r="E208" s="29"/>
       <c r="F208" s="27"/>
@@ -3157,8 +3153,8 @@
     </row>
     <row r="209" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="27"/>
-      <c r="B209" s="45"/>
-      <c r="C209" s="45"/>
+      <c r="B209" s="39"/>
+      <c r="C209" s="39"/>
       <c r="D209" s="27"/>
       <c r="E209" s="29"/>
       <c r="F209" s="27"/>
@@ -3168,8 +3164,8 @@
     </row>
     <row r="210" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="27"/>
-      <c r="B210" s="45"/>
-      <c r="C210" s="45"/>
+      <c r="B210" s="39"/>
+      <c r="C210" s="39"/>
       <c r="D210" s="27"/>
       <c r="E210" s="29"/>
       <c r="F210" s="27"/>
@@ -3179,15 +3175,181 @@
     </row>
   </sheetData>
   <mergeCells count="223">
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B203:C203"/>
-    <mergeCell ref="B204:C204"/>
-    <mergeCell ref="B205:C205"/>
-    <mergeCell ref="B206:C206"/>
-    <mergeCell ref="B207:C207"/>
-    <mergeCell ref="B208:C208"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="B166:C166"/>
     <mergeCell ref="B209:C209"/>
     <mergeCell ref="B210:C210"/>
     <mergeCell ref="A7:A8"/>
@@ -3212,6 +3374,15 @@
     <mergeCell ref="B176:C176"/>
     <mergeCell ref="B177:C177"/>
     <mergeCell ref="B178:C178"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B203:C203"/>
+    <mergeCell ref="B204:C204"/>
+    <mergeCell ref="B205:C205"/>
+    <mergeCell ref="B206:C206"/>
+    <mergeCell ref="B207:C207"/>
+    <mergeCell ref="B208:C208"/>
     <mergeCell ref="B179:C179"/>
     <mergeCell ref="B180:C180"/>
     <mergeCell ref="B181:C181"/>
@@ -3227,181 +3398,6 @@
     <mergeCell ref="B173:C173"/>
     <mergeCell ref="B174:C174"/>
     <mergeCell ref="B175:C175"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B161:C161"/>
-    <mergeCell ref="B162:C162"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="B166:C166"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
